--- a/samples/xlsx-good.xlsx
+++ b/samples/xlsx-good.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Không áp dụng</t>
         </is>
       </c>
     </row>

--- a/samples/xlsx-good.xlsx
+++ b/samples/xlsx-good.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DoanhThu2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NgayVaTyLe" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +50,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +128,115 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Doanh thu theo tháng</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DoanhThu2026'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DoanhThu2026'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DoanhThu2026'!$B$2:$B$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +547,11 @@
           <t>Trạng thái</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Quy tắc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -447,6 +567,11 @@
           <t>Đạt</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>XLSX-01/02/03: bảng sạch từ A1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -462,6 +587,11 @@
           <t>Đạt</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>XLSX-05: trạng thái bằng chữ, không chỉ màu</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -477,6 +607,11 @@
           <t>Vượt</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>XLSX-08: điền đủ, không ô trống</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -490,6 +625,66 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Không áp dụng</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>XLSX-04: ghi sẵn giá trị, không formula</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mốc</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Quy tắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chốt Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>XLSX-09: output ra giá trị thô 2026-07-03 00:00:00 và 0.15</t>
         </is>
       </c>
     </row>

--- a/samples/xlsx-good.xlsx
+++ b/samples/xlsx-good.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XLSX-09: output ra giá trị thô 2026-07-03 00:00:00 và 0.15</t>
+          <t>XLSX-09: ngày &amp; % ra giá trị thô, không theo định dạng hiển thị</t>
         </is>
       </c>
     </row>
